--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-09_Comunicacao_Controlo_Documental.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-09_Comunicacao_Controlo_Documental.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAA1A99-B649-47E0-B53A-66866DA643E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417A4F94-2ACB-4A8E-BBBA-050987054AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
